--- a/Variable descriptions.xlsx
+++ b/Variable descriptions.xlsx
@@ -1,15 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25007"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be89a93bd219aae1/Documentos/student_research/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_FF7330CF566F995279F4AA422DEFE5BAA0F39795" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE1CA764-C3A4-4556-8C1E-B56D3E7BEE7B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14760" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="National level APS variables" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="140000"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -19,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="398">
   <si>
     <t>Variable description</t>
   </si>
@@ -660,6 +667,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUBOANW}</t>
@@ -675,6 +683,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BABYBUyy}</t>
@@ -690,6 +699,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{ESTBBUyy}</t>
@@ -705,6 +715,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {TEAyy}</t>
@@ -720,6 +731,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BUSANGyy}</t>
@@ -735,6 +747,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENyy}</t>
@@ -751,6 +764,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>none</t>
@@ -760,6 +774,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> of the customers </t>
@@ -770,6 +785,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWCS, OMNEWCST}</t>
@@ -786,6 +802,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>few</t>
@@ -795,6 +812,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> businesses offer the same product </t>
@@ -805,6 +823,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUCOMPET, OMCOMPET}</t>
@@ -821,6 +840,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>being independent</t>
@@ -830,6 +850,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> as their main motive </t>
@@ -840,6 +861,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOPTYPE, OMOPTYPE}</t>
@@ -856,6 +878,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">increasing income </t>
@@ -865,6 +888,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">as their main motive </t>
@@ -875,6 +899,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOPTYPE, OMOPTYPE}</t>
@@ -891,6 +916,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>maintaining income</t>
@@ -900,6 +926,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> as their main motive </t>
@@ -910,6 +937,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOPTYPE, OMOPTYPE}</t>
@@ -926,6 +954,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>other issues</t>
@@ -935,6 +964,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> as their main motive </t>
@@ -945,6 +975,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOPTYPE, OMOPTYPE}</t>
@@ -960,6 +991,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -969,6 +1001,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: reporting that main reason was </t>
@@ -980,6 +1013,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>an opportunity to sell the business</t>
@@ -995,6 +1029,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -1004,6 +1039,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: reporting that main reason was </t>
@@ -1015,6 +1051,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>that the business was not profitable</t>
@@ -1030,6 +1067,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -1039,6 +1077,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: reporting that main reason was </t>
@@ -1050,6 +1089,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>problems getting finance</t>
@@ -1065,6 +1105,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -1074,6 +1115,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: reporting that main reason was</t>
@@ -1085,6 +1127,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> another job or business opportunity</t>
@@ -1100,6 +1143,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -1109,6 +1153,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: reporting that main reason was </t>
@@ -1120,6 +1165,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>that the exit was planned in advance</t>
@@ -1135,6 +1181,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -1144,6 +1191,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>:</t>
@@ -1153,6 +1201,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> reporting that main reason was </t>
@@ -1164,6 +1213,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>retirement</t>
@@ -1179,6 +1229,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -1188,6 +1239,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: reporting that main reason was </t>
@@ -1199,6 +1251,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>of a personal nature</t>
@@ -1214,6 +1267,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{DISCENTyy}</t>
@@ -1223,6 +1277,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>:</t>
@@ -1232,6 +1287,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> reporting that main reason was</t>
@@ -1242,6 +1298,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> t</t>
@@ -1253,6 +1310,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>he consequence of a single incident</t>
@@ -1272,6 +1330,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>employeed</t>
@@ -1281,6 +1340,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> respondents (18-64): active and leading as intrapreneur in past three years (2011 SPECIAL TOPIC, 2012 OPTIONAL)</t>
@@ -1300,6 +1360,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>employeed</t>
@@ -1309,6 +1370,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> respondents (18-64): active and leading as intrapreneur now (2011 SPECIAL TOPIC, 2012 OPTIONAL)</t>
@@ -1334,6 +1396,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>did not continue</t>
@@ -1343,6 +1406,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> its activities </t>
@@ -1359,6 +1423,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>continued</t>
@@ -1368,6 +1433,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> its activities </t>
@@ -1383,6 +1449,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{KNOWENT adapted to  fit national level aggregation}</t>
@@ -1398,6 +1465,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{OPPORT adapted to fit national level aggregation}</t>
@@ -1413,6 +1481,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {SUSKILL adapted to fit national level aggregation}</t>
@@ -1428,6 +1497,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {FEARFAIL adapted to fit national level aggregation}</t>
@@ -1443,6 +1513,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{EQUALINC adapted to fit national level aggregation}</t>
@@ -1452,6 +1523,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (OPTIONAL VARIABLE)</t>
@@ -1467,6 +1539,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">{NBGOODC adapted to fit national level aggregation} </t>
@@ -1476,6 +1549,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(OPTIONAL VARIABLE)</t>
@@ -1491,6 +1565,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{NBSTATUS adapted to fit national level aggregation}</t>
@@ -1500,6 +1575,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (OPTIONAL VARIABLE)</t>
@@ -1515,6 +1591,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{NBMEDIA adapted to fit national level aggregation}</t>
@@ -1524,6 +1601,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (OPTIONAL VARIABLE)</t>
@@ -1539,6 +1617,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BSTART}</t>
@@ -1548,6 +1627,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or a start-up sponsored by an existing business </t>
@@ -1558,6 +1638,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BJOBST}</t>
@@ -1573,6 +1654,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BSTART}</t>
@@ -1582,6 +1664,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or a start-up sponsored by an existing business </t>
@@ -1592,6 +1675,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BJOBST}</t>
@@ -1601,6 +1685,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> that expect to own all or part of the new firm </t>
@@ -1611,6 +1696,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOWN}</t>
@@ -1626,6 +1712,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BSTART}</t>
@@ -1635,6 +1722,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or a start-up sponsored by an existing business </t>
@@ -1645,6 +1733,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BJOBST}</t>
@@ -1654,6 +1743,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> that expect to own all or part of the new firm </t>
@@ -1664,6 +1754,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOWN}</t>
@@ -1673,6 +1764,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and have paid no salaries or wages for more than three months </t>
@@ -1683,6 +1775,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUWAGE}</t>
@@ -1697,6 +1790,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(“yy” represents 2-digit year indicator)</t>
@@ -1712,6 +1806,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUBOANW}</t>
@@ -1720,6 +1815,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>,</t>
@@ -1729,6 +1825,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> owner-manager of a baby business </t>
@@ -1739,6 +1836,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BAYBYBUSO}</t>
@@ -1748,6 +1846,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or owner-manager of an established businesses </t>
@@ -1758,6 +1857,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{ESTBBUSO}</t>
@@ -1773,6 +1873,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BABYBUSO}</t>
@@ -1782,6 +1883,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or an established firm </t>
@@ -1792,6 +1894,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{ESTBBUSO},</t>
@@ -1801,6 +1904,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1812,6 +1916,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>including agriculture.</t>
@@ -1827,6 +1932,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BABYBUSO}</t>
@@ -1836,6 +1942,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or an established firm </t>
@@ -1846,6 +1953,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">{ESTBBUSO}, </t>
@@ -1857,6 +1965,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>excluding agriculture.</t>
@@ -1872,6 +1981,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUBOANW}</t>
@@ -1881,6 +1991,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or young firm </t>
@@ -1891,6 +2002,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{BABYBUSO}</t>
@@ -1900,6 +2012,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or both (if doing both, still counted as one active person). TEA is slightly lower than total of BABYBUyy and SUBOANyy. </t>
@@ -1910,6 +2023,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>[TOTAL ENTREPRENEURIAL ACTIVITY (TEA) INDEX]</t>
@@ -1926,6 +2040,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>opportunity</t>
@@ -1935,6 +2050,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> as major motive. </t>
@@ -1962,6 +2078,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">[ESTABLISHED BUSINESS </t>
@@ -1973,6 +2090,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>MALE</t>
@@ -1983,6 +2101,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -1998,6 +2117,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">[ESTABLISHED BUSINESS </t>
@@ -2009,6 +2129,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>FEMALE</t>
@@ -2019,6 +2140,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -2034,6 +2156,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">[TOTAL ENTREPRENEURIAL ACTIVITY (TEA) INDEX </t>
@@ -2045,6 +2168,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>MALE</t>
@@ -2055,6 +2179,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -2070,6 +2195,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">[TOTAL ENTREPRENEURIAL ACTIVITY (TEA) INDEX </t>
@@ -2081,6 +2207,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>FEMALE</t>
@@ -2091,6 +2218,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -2107,6 +2235,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>necessity</t>
@@ -2116,6 +2245,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (no better choice for work) as major motive. </t>
@@ -2131,6 +2261,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2140,6 +2271,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: primarily motivated by</t>
@@ -2150,6 +2282,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2161,6 +2294,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>increasing income</t>
@@ -2171,6 +2305,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -2180,6 +2315,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -2190,6 +2326,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUREASON, OMREASON, SUOPTYPE, OMOPTYPE}</t>
@@ -2205,6 +2342,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2214,6 +2352,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: primarily motivated by </t>
@@ -2225,6 +2364,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>being independent</t>
@@ -2235,6 +2375,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -2244,6 +2385,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -2254,6 +2396,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUREASON, OMREASON, SUOPTYPE, OMOPTYPE}</t>
@@ -2269,6 +2412,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2278,6 +2422,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: primarily motivated by </t>
@@ -2289,6 +2434,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>mixed motivations</t>
@@ -2299,6 +2445,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2309,6 +2456,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{answers 3+4 in SUREASON, OMREASON}.</t>
@@ -2324,6 +2472,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2333,6 +2482,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: primarily motivated by</t>
@@ -2343,6 +2493,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2354,6 +2505,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>non-opportunity motivations (either necessity or ‘maintaining income)</t>
@@ -2363,6 +2515,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2373,6 +2526,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOPTYPE, OMOPTYPE}</t>
@@ -2388,6 +2542,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUBOANyy}</t>
@@ -2397,6 +2552,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and motivated by opportunity </t>
@@ -2407,6 +2563,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUREASON}</t>
@@ -2422,6 +2579,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUBOANyy}</t>
@@ -2431,6 +2589,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and motivated by necessity </t>
@@ -2441,6 +2600,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUREASON}</t>
@@ -2456,6 +2616,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2465,6 +2626,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: whose business is in the </t>
@@ -2476,6 +2638,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>extractive sector</t>
@@ -2485,6 +2648,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (agriculture, forestry, fishing, and all mining). </t>
@@ -2500,6 +2664,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2509,6 +2674,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: whose business is in the</t>
@@ -2520,6 +2686,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> transformative sector</t>
@@ -2529,6 +2696,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (construction, manufacturing, transportation, communication, utilities, and wholesale).</t>
@@ -2544,6 +2712,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2553,6 +2722,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: whose business is in the </t>
@@ -2564,6 +2734,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>business services</t>
@@ -2573,6 +2744,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (finance, insurance, real estate, all business services). </t>
@@ -2588,6 +2760,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2597,6 +2770,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: whose business is in the </t>
@@ -2608,6 +2782,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>extractive sector</t>
@@ -2617,6 +2792,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (agriculture, forestry, fishing, and all mining). </t>
@@ -2632,6 +2808,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2641,6 +2818,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: whose business is in </t>
@@ -2652,6 +2830,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>consumer services</t>
@@ -2661,6 +2840,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (retail, motor vehicles, lodging, restaurants, personal services, health, education and social services, recreational services). </t>
@@ -2676,6 +2856,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2685,6 +2866,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: whose business is in the </t>
@@ -2696,6 +2878,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>business services</t>
@@ -2705,6 +2888,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (finance, insurance, real estate, all business services). </t>
@@ -2720,6 +2904,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2729,6 +2914,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: whose business is in the</t>
@@ -2740,6 +2926,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> transformative sector</t>
@@ -2749,6 +2936,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (construction, manufacturing, transportation, communication, utilities, and wholesale).</t>
@@ -2764,6 +2952,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2773,6 +2962,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: whose business is in </t>
@@ -2784,6 +2974,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>consumer services</t>
@@ -2793,6 +2984,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (retail, motor vehicles, lodging, restaurants, personal services, health, education and social services, recreational services). </t>
@@ -2808,6 +3000,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2817,6 +3010,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> SU: </t>
@@ -2828,6 +3022,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no</t>
@@ -2837,6 +3032,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside country</t>
@@ -2852,6 +3048,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2861,6 +3058,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: </t>
@@ -2872,6 +3070,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no</t>
@@ -2881,6 +3080,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside the country</t>
@@ -2896,6 +3096,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2905,6 +3106,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: </t>
@@ -2916,6 +3118,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no</t>
@@ -2925,6 +3128,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside the country</t>
@@ -2940,6 +3144,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2949,6 +3154,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> ANY (Any Business): </t>
@@ -2960,6 +3166,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no</t>
@@ -2969,6 +3176,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside the country</t>
@@ -2987,6 +3195,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -2996,6 +3205,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> ANY (Any Business): </t>
@@ -3007,6 +3217,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1-25%</t>
@@ -3016,6 +3227,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside the country</t>
@@ -3031,6 +3243,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3040,6 +3253,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> ANY (Any Business): </t>
@@ -3051,6 +3265,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>25-75%</t>
@@ -3060,6 +3275,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside country</t>
@@ -3075,6 +3291,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3084,6 +3301,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> ANY (Any Business): </t>
@@ -3095,6 +3313,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>75-100%</t>
@@ -3104,6 +3323,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside country</t>
@@ -3119,6 +3339,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3128,6 +3349,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: </t>
@@ -3139,6 +3361,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>75-100%</t>
@@ -3148,6 +3371,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside country</t>
@@ -3163,6 +3387,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3172,6 +3397,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: </t>
@@ -3183,6 +3409,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>25-75%</t>
@@ -3192,6 +3419,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside country</t>
@@ -3207,6 +3435,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3216,6 +3445,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: </t>
@@ -3227,6 +3457,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1-25%</t>
@@ -3236,6 +3467,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside the country</t>
@@ -3251,6 +3483,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3260,6 +3493,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: </t>
@@ -3271,6 +3505,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>75-100%</t>
@@ -3280,6 +3515,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside country</t>
@@ -3295,6 +3531,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3304,6 +3541,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: </t>
@@ -3315,6 +3553,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>25-75%</t>
@@ -3324,6 +3563,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside country</t>
@@ -3339,6 +3579,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3348,6 +3589,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: </t>
@@ -3359,6 +3601,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1-25%</t>
@@ -3368,6 +3611,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers outside the country</t>
@@ -3383,6 +3627,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3392,6 +3637,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> SU: </t>
@@ -3403,6 +3649,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>75-100%</t>
@@ -3412,6 +3659,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> of customers outside country</t>
@@ -3427,6 +3675,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3436,6 +3685,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> SU: </t>
@@ -3447,6 +3697,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>25-75%</t>
@@ -3456,6 +3707,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> of customers outside country</t>
@@ -3471,6 +3723,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3480,6 +3733,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> SU: </t>
@@ -3491,6 +3745,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1-25%</t>
@@ -3500,6 +3755,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> of customers outside country</t>
@@ -3516,6 +3772,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1</t>
@@ -3525,6 +3782,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3541,6 +3799,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2</t>
@@ -3550,6 +3809,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3566,6 +3826,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3</t>
@@ -3575,6 +3836,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3591,6 +3853,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>4</t>
@@ -3600,6 +3863,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3616,6 +3880,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1</t>
@@ -3625,6 +3890,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3641,6 +3907,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2</t>
@@ -3650,6 +3917,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3666,6 +3934,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3</t>
@@ -3675,6 +3944,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3691,6 +3961,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>4</t>
@@ -3700,6 +3971,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in impact in terms of market expansion on a four-point index [1-4; 4 highest]. </t>
@@ -3718,6 +3990,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3727,6 +4000,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: expecting 10 or more jobs 5 years after the business has started (or 5 years from now on if the business is already operational – in that case an extra requirement is that job growth is at least 50%). [HIGH JOB EXPECTATIONS]</t>
@@ -3742,6 +4016,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3751,6 +4026,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: expecting 10 or more jobs 5 years after the business has started (or 5 years from now on if the business is already operational – in that case an extra requirement is that job growth is at least 50%).   [HIGH JOB EXPECTATIONS]</t>
@@ -3766,6 +4042,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3775,6 +4052,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting some new product/market combination: the product is new to all/most customers </t>
@@ -3785,6 +4063,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWCST, OMNEWCST}</t>
@@ -3794,6 +4073,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> AND there are no/few competitors </t>
@@ -3804,6 +4084,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">{SUCOMPET, OMCOMPET}. </t>
@@ -3819,6 +4100,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3828,6 +4110,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting some new product/market combination: the product is new to all/most customers </t>
@@ -3838,6 +4121,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWCST, OMNEWCST}</t>
@@ -3847,6 +4131,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> AND there are no/few competitors </t>
@@ -3857,6 +4142,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUCOMPET, OMCOMPET}.</t>
@@ -3872,6 +4158,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3881,6 +4168,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting business activity in a technology sector (high or medium), according to OECD classification.</t>
@@ -3896,6 +4184,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3905,6 +4194,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting business activity in a technology sector (high or medium), according to OECD classification.</t>
@@ -3920,6 +4210,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3929,6 +4220,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that their product is new to </t>
@@ -3940,6 +4232,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>all</t>
@@ -3949,6 +4242,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers</t>
@@ -3959,6 +4253,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {SUNEWCS, OMNEWCST}</t>
@@ -3974,6 +4269,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -3983,6 +4279,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that their product is new to </t>
@@ -3994,6 +4291,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>some</t>
@@ -4003,6 +4301,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers </t>
@@ -4013,6 +4312,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWCS, OMNEWCST}</t>
@@ -4028,6 +4328,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4037,6 +4338,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that their product is new to </t>
@@ -4048,6 +4350,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>all</t>
@@ -4057,6 +4360,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers </t>
@@ -4067,6 +4371,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWCS, OMNEWCST}</t>
@@ -4082,6 +4387,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4091,6 +4397,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that their product is new to </t>
@@ -4102,6 +4409,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>some</t>
@@ -4111,6 +4419,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> customers </t>
@@ -4121,6 +4430,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWCS, OMNEWCST}</t>
@@ -4136,6 +4446,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4145,6 +4456,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that </t>
@@ -4156,6 +4468,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>many</t>
@@ -4165,6 +4478,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> businesses offer the same product </t>
@@ -4175,6 +4489,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUCOMPET, OMCOMPET}</t>
@@ -4190,6 +4505,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4199,6 +4515,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that </t>
@@ -4210,6 +4527,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no</t>
@@ -4219,6 +4537,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> businesses offer the same product </t>
@@ -4229,6 +4548,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUCOMPET, OMCOMPET}</t>
@@ -4244,6 +4564,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4253,6 +4574,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB (Established Business): reporting that</t>
@@ -4264,6 +4586,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> many</t>
@@ -4273,6 +4596,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> businesses offer the same product </t>
@@ -4283,6 +4607,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUCOMPET, OMCOMPET}</t>
@@ -4298,6 +4623,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4307,6 +4633,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that </t>
@@ -4318,6 +4645,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>few</t>
@@ -4327,6 +4655,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> businesses offer the same product</t>
@@ -4337,6 +4666,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {SUCOMPET, OMCOMPET}</t>
@@ -4352,6 +4682,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4361,6 +4692,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that </t>
@@ -4372,6 +4704,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no</t>
@@ -4381,6 +4714,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> businesses offer the same product </t>
@@ -4391,6 +4725,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUCOMPET, OMCOMPET}</t>
@@ -4406,6 +4741,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4415,6 +4751,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that they use the</t>
@@ -4426,6 +4763,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> very latest </t>
@@ -4435,6 +4773,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">technology, not available one year ago </t>
@@ -4445,6 +4784,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWTEC, OMNEWTEC}</t>
@@ -4460,6 +4800,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4469,6 +4810,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that they use </t>
@@ -4479,6 +4821,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>new</t>
@@ -4488,6 +4831,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> technology, not available since 1-5 years </t>
@@ -4498,6 +4842,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWTEC, OMNEWTEC}</t>
@@ -4513,6 +4858,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4522,6 +4868,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that they use</t>
@@ -4533,6 +4880,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> no new</t>
@@ -4542,6 +4890,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> technology</t>
@@ -4552,6 +4901,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {SUNEWTEC, OMNEWTEC}</t>
@@ -4567,6 +4917,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4576,6 +4927,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that they use </t>
@@ -4587,6 +4939,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>new</t>
@@ -4596,6 +4949,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> technology, not available since 1-5 years </t>
@@ -4606,6 +4960,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWTEC, OMNEWTEC}</t>
@@ -4621,6 +4976,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4630,6 +4986,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that they use the </t>
@@ -4641,6 +4998,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>very latest</t>
@@ -4650,6 +5008,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> technology, not available one year ago </t>
@@ -4660,6 +5019,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWTEC, OMNEWTEC}</t>
@@ -4675,6 +5035,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4684,6 +5045,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that they use </t>
@@ -4695,6 +5057,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no new</t>
@@ -4704,6 +5067,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> technology </t>
@@ -4714,6 +5078,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWTEC, OMNEWTEC}</t>
@@ -4729,6 +5094,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4738,6 +5104,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: who are </t>
@@ -4749,6 +5116,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>18-24 years old</t>
@@ -4764,6 +5132,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4773,6 +5142,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: who are </t>
@@ -4784,6 +5154,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>25-34 years old</t>
@@ -4799,6 +5170,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4808,6 +5180,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: who are </t>
@@ -4819,6 +5192,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>35-44 years old</t>
@@ -4834,6 +5208,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4843,6 +5218,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: who are </t>
@@ -4854,6 +5230,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>45-54 years old</t>
@@ -4869,6 +5246,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4878,6 +5256,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: who are </t>
@@ -4889,6 +5268,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>55-64 years old</t>
@@ -4904,6 +5284,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4913,6 +5294,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: who are </t>
@@ -4924,6 +5306,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>18-24 years old</t>
@@ -4939,6 +5322,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4948,6 +5332,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: who are </t>
@@ -4959,6 +5344,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>25-34 years old</t>
@@ -4974,6 +5360,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -4983,6 +5370,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: who are </t>
@@ -4994,6 +5382,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>35-44 years old</t>
@@ -5009,6 +5398,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5018,6 +5408,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: who are </t>
@@ -5029,6 +5420,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>45-54 years old</t>
@@ -5044,6 +5436,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5053,6 +5446,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: who are </t>
@@ -5064,6 +5458,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>55-64 years old</t>
@@ -5079,6 +5474,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5088,6 +5484,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting necessity (no better choice for work) as major motive</t>
@@ -5103,6 +5500,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5112,6 +5510,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: expecting more than 5 employees in next five years</t>
@@ -5127,6 +5526,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5136,6 +5536,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting that product is new to all or some customers</t>
@@ -5151,6 +5552,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5160,6 +5562,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting new market (few/no businesses offer the same product)</t>
@@ -5175,6 +5578,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5184,6 +5588,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: with </t>
@@ -5195,6 +5600,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>strong</t>
@@ -5204,6 +5610,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> international orientation (more than 25% of customers from outside country)</t>
@@ -5219,6 +5626,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5228,6 +5636,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: with </t>
@@ -5239,6 +5648,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>weak</t>
@@ -5248,6 +5658,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> international orientation (more than 1% of customers from outside country)</t>
@@ -5278,6 +5689,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -5288,6 +5700,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>[NASCENT FIRM PREVALENCE RATE]</t>
@@ -5303,6 +5716,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>[BABY BUSINESS PREVALENCE RATE]</t>
@@ -5318,6 +5732,7 @@
         <sz val="10"/>
         <color rgb="FFFF6600"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>[ESTABLISHED BUSINESS PREVALENCE RATE]</t>
@@ -5333,6 +5748,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5342,6 +5758,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EB: reporting that their product is new to </t>
@@ -5353,6 +5770,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>none</t>
@@ -5362,6 +5780,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> of the customers </t>
@@ -5372,6 +5791,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUNEWCST, OMNEWCST}</t>
@@ -5387,6 +5807,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -5396,6 +5817,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: </t>
@@ -5406,6 +5828,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with at least post secondary education</t>
@@ -5415,6 +5838,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -5431,6 +5855,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with post- secondary degree as highest qualification:</t>
@@ -5440,6 +5865,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -5456,6 +5882,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with graduate experience as highest qualification:</t>
@@ -5465,6 +5892,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -5481,6 +5909,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">with household income in </t>
@@ -5493,6 +5922,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>lowest</t>
@@ -5504,6 +5934,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 33 percentile:</t>
@@ -5513,6 +5944,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5529,6 +5961,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">with household income in </t>
@@ -5541,6 +5974,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>middle</t>
@@ -5552,6 +5986,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 33 percentile:</t>
@@ -5561,6 +5996,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5577,6 +6013,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">with household income in </t>
@@ -5589,6 +6026,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>highest</t>
@@ -5600,6 +6038,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 33 percentile:</t>
@@ -5609,6 +6048,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5625,6 +6065,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">with household income in </t>
@@ -5637,6 +6078,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>lowest</t>
@@ -5648,6 +6090,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 33 percentile:</t>
@@ -5657,6 +6100,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -5673,6 +6117,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">with household income in </t>
@@ -5685,6 +6130,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>middle</t>
@@ -5696,6 +6142,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 33 percentile:</t>
@@ -5705,6 +6152,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -5721,6 +6169,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">with household income in </t>
@@ -5733,6 +6182,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>highest</t>
@@ -5744,6 +6194,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 33 percentile</t>
@@ -5754,6 +6205,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: </t>
@@ -5763,6 +6215,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -5779,6 +6232,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with secondary degree as highest qualification:</t>
@@ -5788,6 +6242,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -5804,6 +6259,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with some secondary experience as highest qualification:</t>
@@ -5813,6 +6269,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -5829,6 +6286,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with graduate experience as highest qualification:</t>
@@ -5838,6 +6296,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5854,6 +6313,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with post- secondary degree as highest qualification:</t>
@@ -5863,6 +6323,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5879,6 +6340,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with secondary degree as highest qualification:</t>
@@ -5888,6 +6350,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5904,6 +6367,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>with some secondary experience as highest qualification:</t>
@@ -5913,6 +6377,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5929,6 +6394,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>students and retired:</t>
@@ -5938,6 +6404,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5954,6 +6421,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>not working:</t>
@@ -5963,6 +6431,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -5979,6 +6448,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>working:</t>
@@ -5988,6 +6458,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -6004,6 +6475,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>18-24</t>
@@ -6014,6 +6486,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6025,6 +6498,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>years old:</t>
@@ -6034,6 +6508,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in EB</t>
@@ -6050,6 +6525,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>18-24</t>
@@ -6060,6 +6536,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -6071,6 +6548,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>years old:</t>
@@ -6080,6 +6558,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> involved in TEA</t>
@@ -6096,6 +6575,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>25-34 years old</t>
@@ -6105,6 +6585,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in TEA</t>
@@ -6121,6 +6602,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>35-44 years old</t>
@@ -6130,6 +6612,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in TEA</t>
@@ -6146,6 +6629,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>45-54 years old</t>
@@ -6155,6 +6639,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in TEA</t>
@@ -6171,6 +6656,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>55-64 years old</t>
@@ -6180,6 +6666,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in TEA</t>
@@ -6196,6 +6683,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 25-34 years old</t>
@@ -6205,6 +6693,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in EB</t>
@@ -6221,6 +6710,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>35-44 years old</t>
@@ -6230,6 +6720,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in EB</t>
@@ -6246,6 +6737,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>45-54 years old</t>
@@ -6255,6 +6747,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in EB</t>
@@ -6271,6 +6764,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>55-64 years old</t>
@@ -6280,6 +6774,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: involved in EB</t>
@@ -6298,6 +6793,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(TEA)</t>
@@ -6307,6 +6803,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (current number of owners). </t>
@@ -6317,6 +6814,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOWN, OMOWN}</t>
@@ -6332,6 +6830,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(EB)</t>
@@ -6341,6 +6840,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (current number of owners). </t>
@@ -6351,6 +6851,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{OMOWN}</t>
@@ -6366,6 +6867,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(BB)</t>
@@ -6375,6 +6877,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (current number of owners). </t>
@@ -6385,6 +6888,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOWN, OMOWN}</t>
@@ -6400,6 +6904,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(SU)</t>
@@ -6409,6 +6914,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (i.e. expected number of owners). </t>
@@ -6419,6 +6925,7 @@
         <sz val="10"/>
         <color rgb="FF660066"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>{SUOWN, OMOWN}</t>
@@ -6434,6 +6941,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -6443,6 +6951,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting opportunity as major motive (main driver for being involved in this opportunity is being independent or increasing their income, rather than just maintaining their income)</t>
@@ -6461,6 +6970,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>within</t>
@@ -6470,6 +6980,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> TEA: reporting opportunity as major motive</t>
@@ -6489,12 +7000,30 @@
   </si>
   <si>
     <t>Percentage of respondents who were informal investorors in the last 3 years (and provided value of investment)(weighted)</t>
+  </si>
+  <si>
+    <t>separate models for ols and random effects</t>
+  </si>
+  <si>
+    <t>do predictive/lagged models</t>
+  </si>
+  <si>
+    <t>*** for significance at 10%</t>
+  </si>
+  <si>
+    <t>send code and data</t>
+  </si>
+  <si>
+    <t>include Z variables</t>
+  </si>
+  <si>
+    <t>time fixed effects</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -6523,12 +7052,14 @@
       <sz val="12"/>
       <color rgb="FFFF6600"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="9" tint="0.79998168889431442"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6536,12 +7067,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6550,11 +7083,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6562,6 +7097,7 @@
       <sz val="10"/>
       <color rgb="FFFF6600"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6569,6 +7105,7 @@
       <sz val="10"/>
       <color rgb="FF660066"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6576,6 +7113,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6583,6 +7121,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6592,17 +7131,20 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF660066"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6611,6 +7153,7 @@
       <sz val="10"/>
       <color rgb="FFFF6600"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6618,6 +7161,7 @@
       <sz val="9"/>
       <color rgb="FF660066"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -6832,9 +7376,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6853,16 +7396,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6875,22 +7414,19 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="89">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -6985,6 +7521,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -7309,1600 +7853,1599 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C197"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="39" customHeight="1" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="39" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="3.296875" customWidth="1"/>
+    <col min="2" max="2" width="16.796875" customWidth="1"/>
+    <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1">
-      <c r="A1" s="9"/>
-      <c r="B1" s="18" t="s">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
+      <c r="B1" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C1" s="18"/>
-    </row>
-    <row r="2" spans="1:3" ht="15">
-      <c r="A2" s="11"/>
-      <c r="B2" s="18" t="s">
+      <c r="C1" s="15"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="11"/>
-      <c r="B3" s="18" t="s">
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="16" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="11"/>
-      <c r="B4" s="18" t="s">
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16" thickBot="1">
-      <c r="A5" s="11"/>
-      <c r="B5" s="18" t="s">
+    <row r="5" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9"/>
+      <c r="B5" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43" thickBot="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B11" s="14" t="s">
+    <row r="11" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B12" s="14" t="s">
+    <row r="12" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B13" s="14" t="s">
+    <row r="13" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B14" s="14" t="s">
+    <row r="14" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B15" s="14" t="s">
+    <row r="15" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B16" s="14" t="s">
+    <row r="16" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B17" s="14" t="s">
+    <row r="17" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B18" s="17" t="s">
+    <row r="18" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B19" s="17" t="s">
+    <row r="19" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="17" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B20" s="17" t="s">
+    <row r="20" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="17" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B21" s="17" t="s">
+    <row r="21" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="17" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B22" s="14" t="s">
+    <row r="22" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="17" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B23" s="14" t="s">
+    <row r="23" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B24" s="17" t="s">
+    <row r="24" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B25" s="17" t="s">
+    <row r="25" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B26" s="14" t="s">
+    <row r="26" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B27" s="14" t="s">
+    <row r="27" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="A28" s="13"/>
-      <c r="B28" s="17" t="s">
+    <row r="28" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10"/>
+      <c r="B28" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="A29" s="13"/>
-      <c r="B29" s="17" t="s">
+    <row r="29" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10"/>
+      <c r="B29" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B30" s="14" t="s">
+    <row r="30" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B31" s="14" t="s">
+    <row r="31" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B32" s="14" t="s">
+    <row r="32" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B33" s="14" t="s">
+    <row r="33" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B34" s="17" t="s">
+    <row r="34" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B35" s="17" t="s">
+    <row r="35" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="6" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B36" s="17" t="s">
+    <row r="36" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B37" s="17" t="s">
+    <row r="37" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B38" s="17" t="s">
+    <row r="38" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B39" s="17" t="s">
+    <row r="39" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B40" s="17" t="s">
+    <row r="40" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B41" s="14" t="s">
+    <row r="41" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="6" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B42" s="14" t="s">
+    <row r="42" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="6" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B43" s="17" t="s">
+    <row r="43" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="6" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B44" s="17" t="s">
+    <row r="44" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B45" s="17" t="s">
+    <row r="45" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="6" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B46" s="14" t="s">
+    <row r="46" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="6" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B47" s="14" t="s">
+    <row r="47" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B48" s="17" t="s">
+    <row r="48" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="18" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B49" s="17" t="s">
+    <row r="49" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="6" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B50" s="14" t="s">
+    <row r="50" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B51" s="14" t="s">
+    <row r="51" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="6" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B52" s="17" t="s">
+    <row r="52" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="6" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B53" s="17" t="s">
+    <row r="53" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="6" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B54" s="14" t="s">
+    <row r="54" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="6" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B55" s="17" t="s">
+    <row r="55" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="6" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B56" s="17" t="s">
+    <row r="56" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="6" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="57" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B57" s="17" t="s">
+    <row r="57" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="6" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="58" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B58" s="17" t="s">
+    <row r="58" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="6" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="59" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B59" s="14" t="s">
+    <row r="59" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="6" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B60" s="14" t="s">
+    <row r="60" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="6" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="61" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B61" s="17" t="s">
+    <row r="61" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="6" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="62" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B62" s="17" t="s">
+    <row r="62" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="6" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B63" s="17" t="s">
+    <row r="63" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="64" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B64" s="17" t="s">
+    <row r="64" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B65" s="17" t="s">
+    <row r="65" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B66" s="17" t="s">
+    <row r="66" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="6" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B67" s="17" t="s">
+    <row r="67" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B67" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B68" s="14" t="s">
+    <row r="68" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="6" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B69" s="14" t="s">
+    <row r="69" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B69" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="6" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B70" s="14" t="s">
+    <row r="70" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="6" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B71" s="14" t="s">
+    <row r="71" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="6" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="A72" s="13"/>
-      <c r="B72" s="17" t="s">
+    <row r="72" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="10"/>
+      <c r="B72" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="6" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="A73" s="13"/>
-      <c r="B73" s="17" t="s">
+    <row r="73" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="10"/>
+      <c r="B73" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="6" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="A74" s="13"/>
-      <c r="B74" s="17" t="s">
+    <row r="74" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="10"/>
+      <c r="B74" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="6" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="A75" s="13"/>
-      <c r="B75" s="17" t="s">
+    <row r="75" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="10"/>
+      <c r="B75" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="6" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B76" s="14" t="s">
+    <row r="76" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="6" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B77" s="14" t="s">
+    <row r="77" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="6" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B78" s="14" t="s">
+    <row r="78" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="6" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B79" s="14" t="s">
+    <row r="79" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="6" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B80" s="17" t="s">
+    <row r="80" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="81" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B81" s="17" t="s">
+    <row r="81" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="6" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="82" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B82" s="17" t="s">
+    <row r="82" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="6" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="83" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B83" s="17" t="s">
+    <row r="83" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B83" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="84" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B84" s="14" t="s">
+    <row r="84" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="6" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="85" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B85" s="14" t="s">
+    <row r="85" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="6" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="86" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B86" s="14" t="s">
+    <row r="86" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="6" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="87" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B87" s="14" t="s">
+    <row r="87" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="6" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="88" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B88" s="17" t="s">
+    <row r="88" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="6" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="89" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B89" s="17" t="s">
+    <row r="89" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B89" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="6" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="90" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B90" s="14" t="s">
+    <row r="90" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="6" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="91" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B91" s="14" t="s">
+    <row r="91" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="6" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="92" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B92" s="14" t="s">
+    <row r="92" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="6" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B93" s="14" t="s">
+    <row r="93" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="6" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B94" s="17" t="s">
+    <row r="94" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="6" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="95" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B95" s="17" t="s">
+    <row r="95" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B95" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="6" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="96" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B96" s="17" t="s">
+    <row r="96" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B96" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="6" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="97" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B97" s="17" t="s">
+    <row r="97" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B97" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="6" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="98" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B98" s="14" t="s">
+    <row r="98" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C98" s="8" t="s">
+      <c r="C98" s="6" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B99" s="14" t="s">
+    <row r="99" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="6" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="100" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B100" s="14" t="s">
+    <row r="100" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B100" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="6" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="101" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B101" s="14" t="s">
+    <row r="101" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="6" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="102" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B102" s="17" t="s">
+    <row r="102" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B102" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C102" s="6" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="103" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B103" s="17" t="s">
+    <row r="103" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B103" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="104" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B104" s="17" t="s">
+    <row r="104" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="6" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B105" s="17" t="s">
+    <row r="105" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="6" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="106" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B106" s="14" t="s">
+    <row r="106" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B106" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="6" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="107" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B107" s="14" t="s">
+    <row r="107" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B107" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="6" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="108" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B108" s="17" t="s">
+    <row r="108" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="6" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="109" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B109" s="17" t="s">
+    <row r="109" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B109" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="6" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="110" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B110" s="14" t="s">
+    <row r="110" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B110" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="6" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="111" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B111" s="14" t="s">
+    <row r="111" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B111" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="6" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="112" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B112" s="17" t="s">
+    <row r="112" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B112" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B113" s="17" t="s">
+    <row r="113" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B113" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C113" s="6" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="114" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B114" s="14" t="s">
+    <row r="114" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B114" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="C114" s="6" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="115" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B115" s="14" t="s">
+    <row r="115" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="6" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="116" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B116" s="14" t="s">
+    <row r="116" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B116" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C116" s="8" t="s">
+      <c r="C116" s="6" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="117" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B117" s="17" t="s">
+    <row r="117" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B117" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="6" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="118" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B118" s="17" t="s">
+    <row r="118" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="6" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="119" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B119" s="17" t="s">
+    <row r="119" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="6" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="120" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B120" s="14" t="s">
+    <row r="120" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C120" s="8" t="s">
+      <c r="C120" s="6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="121" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B121" s="14" t="s">
+    <row r="121" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B121" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="122" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B122" s="14" t="s">
+    <row r="122" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B122" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="6" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="123" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B123" s="17" t="s">
+    <row r="123" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B123" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="6" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="124" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B124" s="17" t="s">
+    <row r="124" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="6" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="125" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B125" s="17" t="s">
+    <row r="125" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="6" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="126" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B126" s="14" t="s">
+    <row r="126" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="6" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="127" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B127" s="14" t="s">
+    <row r="127" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B127" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="6" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="128" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B128" s="14" t="s">
+    <row r="128" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B128" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="6" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="129" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B129" s="17" t="s">
+    <row r="129" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B129" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="6" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="130" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B130" s="17" t="s">
+    <row r="130" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B130" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="6" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="131" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B131" s="17" t="s">
+    <row r="131" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B131" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="6" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="132" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B132" s="14" t="s">
+    <row r="132" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B132" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="133" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B133" s="14" t="s">
+    <row r="133" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B133" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="6" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="134" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B134" s="14" t="s">
+    <row r="134" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B134" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="6" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="135" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B135" s="14" t="s">
+    <row r="135" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B135" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="6" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="136" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B136" s="14" t="s">
+    <row r="136" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B136" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="137" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B137" s="17" t="s">
+    <row r="137" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B137" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="6" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="138" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B138" s="17" t="s">
+    <row r="138" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B138" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="139" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B139" s="17" t="s">
+    <row r="139" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B139" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="6" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="140" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B140" s="17" t="s">
+    <row r="140" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B140" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="6" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="141" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B141" s="17" t="s">
+    <row r="141" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B141" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="6" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="142" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B142" s="14" t="s">
+    <row r="142" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B142" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="6" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="143" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B143" s="14" t="s">
+    <row r="143" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="144" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B144" s="14" t="s">
+    <row r="144" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B144" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="6" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="145" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B145" s="14" t="s">
+    <row r="145" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B145" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="6" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="146" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B146" s="14" t="s">
+    <row r="146" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="6" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="147" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B147" s="17" t="s">
+    <row r="147" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="148" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B148" s="17" t="s">
+    <row r="148" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B148" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="6" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B149" s="17" t="s">
+    <row r="149" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="150" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B150" s="17" t="s">
+    <row r="150" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B150" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="6" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="151" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B151" s="17" t="s">
+    <row r="151" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B151" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="6" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="152" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B152" s="14" t="s">
+    <row r="152" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="153" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B153" s="14" t="s">
+    <row r="153" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="6" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="154" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B154" s="14" t="s">
+    <row r="154" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B154" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="6" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="155" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B155" s="17" t="s">
+    <row r="155" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B155" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="156" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B156" s="17" t="s">
+    <row r="156" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="6" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="157" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B157" s="17" t="s">
+    <row r="157" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="6" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="158" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B158" s="17" t="s">
+    <row r="158" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B158" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C158" s="8" t="s">
+      <c r="C158" s="6" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="159" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B159" s="14" t="s">
+    <row r="159" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B159" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="160" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B160" s="14" t="s">
+    <row r="160" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B160" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="6" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="161" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B161" s="14" t="s">
+    <row r="161" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B161" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C161" s="8" t="s">
+      <c r="C161" s="6" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="162" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B162" s="14" t="s">
+    <row r="162" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B162" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="6" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="163" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B163" s="17" t="s">
+    <row r="163" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B163" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C163" s="8" t="s">
+      <c r="C163" s="6" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="164" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B164" s="14" t="s">
+    <row r="164" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B164" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C164" s="8" t="s">
+      <c r="C164" s="6" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="165" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B165" s="14" t="s">
+    <row r="165" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B165" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="6" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="166" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B166" s="14" t="s">
+    <row r="166" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B166" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="167" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B167" s="14" t="s">
+    <row r="167" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B167" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="6" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="168" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B168" s="14" t="s">
+    <row r="168" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B168" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C168" s="8" t="s">
+      <c r="C168" s="6" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="169" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B169" s="14" t="s">
+    <row r="169" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B169" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C169" s="8" t="s">
+      <c r="C169" s="6" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="170" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B170" s="17" t="s">
+    <row r="170" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B170" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="6" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="171" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B171" s="17" t="s">
+    <row r="171" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B171" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="C171" s="8" t="s">
+      <c r="C171" s="6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="172" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B172" s="17" t="s">
+    <row r="172" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B172" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="C172" s="8" t="s">
+      <c r="C172" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="173" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B173" s="17" t="s">
+    <row r="173" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B173" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C173" s="8" t="s">
+      <c r="C173" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="174" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B174" s="14" t="s">
+    <row r="174" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B174" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C174" s="8" t="s">
+      <c r="C174" s="6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="175" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B175" s="14" t="s">
+    <row r="175" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B175" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="6" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="176" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B176" s="14" t="s">
+    <row r="176" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B176" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C176" s="8" t="s">
+      <c r="C176" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="177" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B177" s="14" t="s">
+    <row r="177" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B177" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="178" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B178" s="14" t="s">
+    <row r="178" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B178" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="6" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="179" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B179" s="14" t="s">
+    <row r="179" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B179" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C179" s="8" t="s">
+      <c r="C179" s="6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="180" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B180" s="14" t="s">
+    <row r="180" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B180" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C180" s="8" t="s">
+      <c r="C180" s="6" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="181" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B181" s="14" t="s">
+    <row r="181" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B181" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="C181" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="182" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B182" s="16" t="s">
+    <row r="182" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B182" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C182" s="22" t="s">
+      <c r="C182" s="4" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="183" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B183" s="16" t="s">
+    <row r="183" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B183" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="C183" s="22" t="s">
+      <c r="C183" s="4" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="184" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B184" s="17" t="s">
+    <row r="184" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B184" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C184" s="8" t="s">
+      <c r="C184" s="6" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="185" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B185" s="17" t="s">
+    <row r="185" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B185" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C185" s="8" t="s">
+      <c r="C185" s="6" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="186" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B186" s="17" t="s">
+    <row r="186" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B186" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C186" s="8" t="s">
+      <c r="C186" s="6" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="187" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B187" s="17" t="s">
+    <row r="187" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="C187" s="8" t="s">
+      <c r="C187" s="6" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="188" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B188" s="17" t="s">
+    <row r="188" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B188" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C188" s="8" t="s">
+      <c r="C188" s="6" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="189" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B189" s="15" t="s">
+    <row r="189" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B189" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C189" s="22" t="s">
+      <c r="C189" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="190" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B190" s="14" t="s">
+    <row r="190" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B190" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C190" s="8" t="s">
+      <c r="C190" s="6" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B191" s="14" t="s">
+    <row r="191" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B191" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="C191" s="8" t="s">
+      <c r="C191" s="6" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="192" spans="2:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B192" s="14" t="s">
+    <row r="192" spans="2:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B192" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C192" s="8" t="s">
+      <c r="C192" s="6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B193" s="14" t="s">
+    <row r="193" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B193" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C193" s="8" t="s">
+      <c r="C193" s="6" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B194" s="16" t="s">
+    <row r="194" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B194" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C194" s="22" t="s">
+      <c r="C194" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B195" s="17" t="s">
+    <row r="195" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B195" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C195" s="8" t="s">
+      <c r="C195" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="B196" s="17" t="s">
+    <row r="196" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B196" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C196" s="8" t="s">
+      <c r="C196" s="6" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="39" customHeight="1" thickBot="1">
-      <c r="A197" s="23"/>
-      <c r="B197" s="17" t="s">
+    <row r="197" spans="1:3" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A197" s="19"/>
+      <c r="B197" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C197" s="8" t="s">
+      <c r="C197" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -8915,4 +9458,44 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2A2A7A-4CB0-4A75-98DC-4F7A44694F59}">
+  <dimension ref="B3:B8"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>